--- a/SPREADSHEETS/TEMPLATE_V2_1YR_CONNECTED.xlsx
+++ b/SPREADSHEETS/TEMPLATE_V2_1YR_CONNECTED.xlsx
@@ -38173,7 +38173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU38"/>
+  <dimension ref="A1:DU44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39279,6 +39279,198 @@
         <is>
           <t>2000.0</t>
         </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_ENABLED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E39">
+        <f>IF(F39="",E38,IF(F39&gt;0,E38+F39,E38))</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>IFERROR(VLOOKUP($A39&amp;"="&amp;$B39,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>IFERROR(VLOOKUP($A39,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E39,"")</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>IFERROR(VLOOKUP($A39,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>IF(B39=C39,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_BAND_PCT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E40">
+        <f>IF(F40="",E39,IF(F40&gt;0,E39+F40,E39))</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>IFERROR(VLOOKUP($A40&amp;"="&amp;$B40,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IFERROR(VLOOKUP($A40,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E40,"")</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>IFERROR(VLOOKUP($A40,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>IF(B40=C40,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_MAX_AGE_MIN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="E41">
+        <f>IF(F41="",E40,IF(F41&gt;0,E40+F41,E40))</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>IFERROR(VLOOKUP($A41&amp;"="&amp;$B41,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>IFERROR(VLOOKUP($A41,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E41,"")</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>IFERROR(VLOOKUP($A41,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>IF(B41=C41,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_REQUIRE_WT_CROSS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>IF(F42="",E41,IF(F42&gt;0,E41+F42,E41))</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>IFERROR(VLOOKUP($A42&amp;"="&amp;$B42,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IFERROR(VLOOKUP($A42,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E42,"")</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>IFERROR(VLOOKUP($A42,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>IF(B42=C42,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_SIZE_PCT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>IF(F43="",E42,IF(F43&gt;0,E42+F43,E42))</f>
+        <v/>
+      </c>
+      <c r="F43">
+        <f>IFERROR(VLOOKUP($A43&amp;"="&amp;$B43,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>IFERROR(VLOOKUP($A43,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E43,"")</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>IFERROR(VLOOKUP($A43,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>IF(B43=C43,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RECOVERY_AUGMENT_ONE_FIRE_PER_REDUCE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E44">
+        <f>IF(F44="",E43,IF(F44&gt;0,E43+F44,E43))</f>
+        <v/>
+      </c>
+      <c r="F44">
+        <f>IFERROR(VLOOKUP($A44&amp;"="&amp;$B44,Results_30d_Deltas!$A$2:$H$5000,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>IFERROR(VLOOKUP($A44,Results_30d_Deltas!$A$2:$H$5000,7,FALSE)-E44,"")</f>
+        <v/>
+      </c>
+      <c r="H44">
+        <f>IFERROR(VLOOKUP($A44,Results_30d_Deltas!$A$2:$H$5000,6,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>IF(B44=C44,"YES","NO")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
